--- a/teste notas.xlsx
+++ b/teste notas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20343"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\teste_de_softer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEAD2CF9-B938-4E39-A830-DE04022087EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5FCC9B-85C6-4B42-A46B-6F4BD4E18190}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{02737E4E-BC58-44DE-9B3E-B7080455028A}"/>
   </bookViews>

--- a/teste notas.xlsx
+++ b/teste notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\teste_de_softer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5FCC9B-85C6-4B42-A46B-6F4BD4E18190}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC6E7E-9268-458E-ADF6-A5404E36C967}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{02737E4E-BC58-44DE-9B3E-B7080455028A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
   <si>
     <t>TIPO DE TESTE</t>
   </si>
@@ -106,13 +106,79 @@
   </si>
   <si>
     <t xml:space="preserve">Testando com um numero maior que 10 </t>
+  </si>
+  <si>
+    <t>[8, 10]</t>
+  </si>
+  <si>
+    <t>calcular_media</t>
+  </si>
+  <si>
+    <t>boletim.calculos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste com notas inteiras </t>
+  </si>
+  <si>
+    <t>Teste com notas decimais</t>
+  </si>
+  <si>
+    <t>Teste com notas negativa</t>
+  </si>
+  <si>
+    <t>Teste com notas acima de 20</t>
+  </si>
+  <si>
+    <t>[2,7 , 3,9]</t>
+  </si>
+  <si>
+    <t>5.25</t>
+  </si>
+  <si>
+    <t>[-6,-4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                      -5.0</t>
+  </si>
+  <si>
+    <t>[22,27]</t>
+  </si>
+  <si>
+    <t>ValueError:"As notas devem ser entre 0 e 10."</t>
+  </si>
+  <si>
+    <t>Teste com todas as notas impares ate 10</t>
+  </si>
+  <si>
+    <t>[1, 3, 5, 7, 9]</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>Teste com todas as notas pares ate 10</t>
+  </si>
+  <si>
+    <t>[2, 4, 6, 8, 10]</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste com notas de 0 a 1 </t>
+  </si>
+  <si>
+    <t>[0,5 , 0,4]</t>
+  </si>
+  <si>
+    <t>2.25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,8 +193,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,25 +234,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECCCFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -218,51 +322,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -584,11 +707,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC16A43A-2272-4B4B-A625-A580A4EDCA87}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="51.28515625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -596,287 +719,463 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="9">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="10">
         <v>4</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="9">
+        <v>6</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="10">
         <v>7</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="9">
         <v>5</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="10">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="9"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="7">
         <v>-5</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="15">
         <v>2000</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
